--- a/analysis/excel/cumulative_retention.xlsx
+++ b/analysis/excel/cumulative_retention.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adam/DataGripProjects/olist-cohort-analysis/analysis/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDBAC958-CB83-2A40-B672-6BC47E7D0B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918AF7B7-3F90-DC40-96FF-6D77ED2671CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3620" yWindow="600" windowWidth="38400" windowHeight="41020" xr2:uid="{FFB4930C-C763-C84A-B491-5777D21231B9}"/>
+    <workbookView xWindow="1100" yWindow="740" windowWidth="45560" windowHeight="41020" xr2:uid="{FFB4930C-C763-C84A-B491-5777D21231B9}"/>
   </bookViews>
   <sheets>
     <sheet name="cumulative_retention_final" sheetId="23" r:id="rId1"/>
@@ -19,6 +19,9 @@
     <definedName name="ExternalData_19" localSheetId="0" hidden="1">cumulative_retention_final!$A$1:$E$82</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="4" r:id="rId2"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -95,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
   <si>
     <t>cohort_month</t>
   </si>
@@ -111,6 +114,15 @@
   <si>
     <t>cumulative_retention</t>
   </si>
+  <si>
+    <t>Average of cumulative_retention</t>
+  </si>
+  <si>
+    <t>Months since first purchase</t>
+  </si>
+  <si>
+    <t>Cohort Months</t>
+  </si>
 </sst>
 </file>
 
@@ -125,12 +137,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF4149"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -145,19 +163,125 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="14">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF4149"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF4149"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF4149"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF4149"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF4149"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF4149"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF4149"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yy"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF4149"/>
+      <color rgb="FFE20002"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -167,6 +291,5265 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[cumulative_retention.xlsx]cumulative_retention_final!PivotTable2</c:name>
+    <c:fmtId val="5"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>Cumulative Customer Retention by Cohort</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-DE"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-DE"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-DE"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-DE"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-DE"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-DE"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-DE"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-DE"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-DE"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>cumulative_retention_final!$H$14:$H$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>01.01.17</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>cumulative_retention_final!$G$16:$G$24</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>cumulative_retention_final!$H$16:$H$24</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.7889999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.5789999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.9740000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.1158E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.2552000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.6736000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.6736000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.8131000000000001E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BB09-994F-9B8D-2C20DAB7CE88}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>cumulative_retention_final!$I$14:$I$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>01.02.17</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>cumulative_retention_final!$G$16:$G$24</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>cumulative_retention_final!$I$16:$I$24</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.843E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.914E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.143E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.0442E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.1671000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.4128E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.5356E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.6584999999999999E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-BB09-994F-9B8D-2C20DAB7CE88}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>cumulative_retention_final!$J$14:$J$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>01.03.17</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>cumulative_retention_final!$G$16:$G$24</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>cumulative_retention_final!$J$16:$J$24</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.3949999999999996E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.9900000000000006E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.1586000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.4782E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.5980999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.7579000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.0774999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.3571999999999999E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-BB09-994F-9B8D-2C20DAB7CE88}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>cumulative_retention_final!$K$14:$K$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>01.04.17</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>cumulative_retention_final!$G$16:$G$24</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>cumulative_retention_final!$K$16:$K$24</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.2059999999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.4220000000000007E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0194999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.2855E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.5514E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.8617000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.172E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.4823000000000001E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-BB09-994F-9B8D-2C20DAB7CE88}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>cumulative_retention_final!$L$14:$L$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>01.05.17</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>cumulative_retention_final!$G$16:$G$24</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>cumulative_retention_final!$L$16:$L$24</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.6360000000000004E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.273E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.1591000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.4199E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.6517E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.9994000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.1443E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.3470999999999999E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-BB09-994F-9B8D-2C20DAB7CE88}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>cumulative_retention_final!$M$14:$M$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>01.06.17</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>cumulative_retention_final!$G$16:$G$24</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>cumulative_retention_final!$M$16:$M$24</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.9389999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.5609999999999992E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.2182999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.4159E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.7451000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.0743999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.3049E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.4365999999999999E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-BB09-994F-9B8D-2C20DAB7CE88}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>cumulative_retention_final!$N$14:$N$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>01.07.17</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>cumulative_retention_final!$G$16:$G$24</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>cumulative_retention_final!$N$16:$N$24</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.3299999999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.5290000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0661E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.3325999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.5458E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.8657E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.9723000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.1588E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-BB09-994F-9B8D-2C20DAB7CE88}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>cumulative_retention_final!$O$14:$O$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>01.08.17</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>cumulative_retention_final!$G$16:$G$24</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>cumulative_retention_final!$O$16:$O$24</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.9020000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0106E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.2324E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.5775000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.0212000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.2922999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.4895E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.5881000000000001E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-BB09-994F-9B8D-2C20DAB7CE88}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>cumulative_retention_final!$P$14:$P$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>01.09.17</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>cumulative_retention_final!$G$16:$G$24</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>cumulative_retention_final!$P$16:$P$24</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.9930000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.1988E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.4486000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.8232000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.0230000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.1728000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.3477000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.5974000000000001E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-BB09-994F-9B8D-2C20DAB7CE88}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="230453951"/>
+        <c:axId val="230455743"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="230453951"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                    <a:effectLst/>
+                  </a:rPr>
+                  <a:t>Months Since First Purchase</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-DE"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="230455743"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="230455743"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                    <a:effectLst/>
+                  </a:rPr>
+                  <a:t>Cumulative Retention Rate (%)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-DE"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="230453951"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>800100</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>203199</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>618066</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>194733</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D5632FD-2014-E7FA-E105-E0CE5D33311D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Adam Czapla" refreshedDate="46136.756284722222" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="81" xr:uid="{434ED5B9-DA2E-A041-949C-A61ADD76EFCC}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="cumulative_retention_final_"/>
+  </cacheSource>
+  <cacheFields count="7">
+    <cacheField name="cohort_month" numFmtId="14">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2017-01-01T00:00:00" maxDate="2017-09-02T00:00:00" count="9">
+        <d v="2017-01-01T00:00:00"/>
+        <d v="2017-02-01T00:00:00"/>
+        <d v="2017-03-01T00:00:00"/>
+        <d v="2017-04-01T00:00:00"/>
+        <d v="2017-05-01T00:00:00"/>
+        <d v="2017-06-01T00:00:00"/>
+        <d v="2017-07-01T00:00:00"/>
+        <d v="2017-08-01T00:00:00"/>
+        <d v="2017-09-01T00:00:00"/>
+      </sharedItems>
+      <fieldGroup par="6"/>
+    </cacheField>
+    <cacheField name="month_number" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="8" count="9">
+        <n v="0"/>
+        <n v="1"/>
+        <n v="2"/>
+        <n v="3"/>
+        <n v="4"/>
+        <n v="5"/>
+        <n v="6"/>
+        <n v="7"/>
+        <n v="8"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="cumulative_count" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="105"/>
+    </cacheField>
+    <cacheField name="cohort_size" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="717" maxValue="4057"/>
+    </cacheField>
+    <cacheField name="cumulative_retention" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="2.5974000000000001E-2"/>
+    </cacheField>
+    <cacheField name="Days (cohort_month)" numFmtId="0" databaseField="0">
+      <fieldGroup base="0">
+        <rangePr groupBy="days" startDate="2017-01-01T00:00:00" endDate="2017-09-02T00:00:00"/>
+        <groupItems count="368">
+          <s v="&lt;01.01.17"/>
+          <s v="01. Jan"/>
+          <s v="02. Jan"/>
+          <s v="03. Jan"/>
+          <s v="04. Jan"/>
+          <s v="05. Jan"/>
+          <s v="06. Jan"/>
+          <s v="07. Jan"/>
+          <s v="08. Jan"/>
+          <s v="09. Jan"/>
+          <s v="10. Jan"/>
+          <s v="11. Jan"/>
+          <s v="12. Jan"/>
+          <s v="13. Jan"/>
+          <s v="14. Jan"/>
+          <s v="15. Jan"/>
+          <s v="16. Jan"/>
+          <s v="17. Jan"/>
+          <s v="18. Jan"/>
+          <s v="19. Jan"/>
+          <s v="20. Jan"/>
+          <s v="21. Jan"/>
+          <s v="22. Jan"/>
+          <s v="23. Jan"/>
+          <s v="24. Jan"/>
+          <s v="25. Jan"/>
+          <s v="26. Jan"/>
+          <s v="27. Jan"/>
+          <s v="28. Jan"/>
+          <s v="29. Jan"/>
+          <s v="30. Jan"/>
+          <s v="31. Jan"/>
+          <s v="01. Feb"/>
+          <s v="02. Feb"/>
+          <s v="03. Feb"/>
+          <s v="04. Feb"/>
+          <s v="05. Feb"/>
+          <s v="06. Feb"/>
+          <s v="07. Feb"/>
+          <s v="08. Feb"/>
+          <s v="09. Feb"/>
+          <s v="10. Feb"/>
+          <s v="11. Feb"/>
+          <s v="12. Feb"/>
+          <s v="13. Feb"/>
+          <s v="14. Feb"/>
+          <s v="15. Feb"/>
+          <s v="16. Feb"/>
+          <s v="17. Feb"/>
+          <s v="18. Feb"/>
+          <s v="19. Feb"/>
+          <s v="20. Feb"/>
+          <s v="21. Feb"/>
+          <s v="22. Feb"/>
+          <s v="23. Feb"/>
+          <s v="24. Feb"/>
+          <s v="25. Feb"/>
+          <s v="26. Feb"/>
+          <s v="27. Feb"/>
+          <s v="28. Feb"/>
+          <s v="29. Feb"/>
+          <s v="01. Mar"/>
+          <s v="02. Mar"/>
+          <s v="03. Mar"/>
+          <s v="04. Mar"/>
+          <s v="05. Mar"/>
+          <s v="06. Mar"/>
+          <s v="07. Mar"/>
+          <s v="08. Mar"/>
+          <s v="09. Mar"/>
+          <s v="10. Mar"/>
+          <s v="11. Mar"/>
+          <s v="12. Mar"/>
+          <s v="13. Mar"/>
+          <s v="14. Mar"/>
+          <s v="15. Mar"/>
+          <s v="16. Mar"/>
+          <s v="17. Mar"/>
+          <s v="18. Mar"/>
+          <s v="19. Mar"/>
+          <s v="20. Mar"/>
+          <s v="21. Mar"/>
+          <s v="22. Mar"/>
+          <s v="23. Mar"/>
+          <s v="24. Mar"/>
+          <s v="25. Mar"/>
+          <s v="26. Mar"/>
+          <s v="27. Mar"/>
+          <s v="28. Mar"/>
+          <s v="29. Mar"/>
+          <s v="30. Mar"/>
+          <s v="31. Mar"/>
+          <s v="01. Apr"/>
+          <s v="02. Apr"/>
+          <s v="03. Apr"/>
+          <s v="04. Apr"/>
+          <s v="05. Apr"/>
+          <s v="06. Apr"/>
+          <s v="07. Apr"/>
+          <s v="08. Apr"/>
+          <s v="09. Apr"/>
+          <s v="10. Apr"/>
+          <s v="11. Apr"/>
+          <s v="12. Apr"/>
+          <s v="13. Apr"/>
+          <s v="14. Apr"/>
+          <s v="15. Apr"/>
+          <s v="16. Apr"/>
+          <s v="17. Apr"/>
+          <s v="18. Apr"/>
+          <s v="19. Apr"/>
+          <s v="20. Apr"/>
+          <s v="21. Apr"/>
+          <s v="22. Apr"/>
+          <s v="23. Apr"/>
+          <s v="24. Apr"/>
+          <s v="25. Apr"/>
+          <s v="26. Apr"/>
+          <s v="27. Apr"/>
+          <s v="28. Apr"/>
+          <s v="29. Apr"/>
+          <s v="30. Apr"/>
+          <s v="01. May"/>
+          <s v="02. May"/>
+          <s v="03. May"/>
+          <s v="04. May"/>
+          <s v="05. May"/>
+          <s v="06. May"/>
+          <s v="07. May"/>
+          <s v="08. May"/>
+          <s v="09. May"/>
+          <s v="10. May"/>
+          <s v="11. May"/>
+          <s v="12. May"/>
+          <s v="13. May"/>
+          <s v="14. May"/>
+          <s v="15. May"/>
+          <s v="16. May"/>
+          <s v="17. May"/>
+          <s v="18. May"/>
+          <s v="19. May"/>
+          <s v="20. May"/>
+          <s v="21. May"/>
+          <s v="22. May"/>
+          <s v="23. May"/>
+          <s v="24. May"/>
+          <s v="25. May"/>
+          <s v="26. May"/>
+          <s v="27. May"/>
+          <s v="28. May"/>
+          <s v="29. May"/>
+          <s v="30. May"/>
+          <s v="31. May"/>
+          <s v="01. Jun"/>
+          <s v="02. Jun"/>
+          <s v="03. Jun"/>
+          <s v="04. Jun"/>
+          <s v="05. Jun"/>
+          <s v="06. Jun"/>
+          <s v="07. Jun"/>
+          <s v="08. Jun"/>
+          <s v="09. Jun"/>
+          <s v="10. Jun"/>
+          <s v="11. Jun"/>
+          <s v="12. Jun"/>
+          <s v="13. Jun"/>
+          <s v="14. Jun"/>
+          <s v="15. Jun"/>
+          <s v="16. Jun"/>
+          <s v="17. Jun"/>
+          <s v="18. Jun"/>
+          <s v="19. Jun"/>
+          <s v="20. Jun"/>
+          <s v="21. Jun"/>
+          <s v="22. Jun"/>
+          <s v="23. Jun"/>
+          <s v="24. Jun"/>
+          <s v="25. Jun"/>
+          <s v="26. Jun"/>
+          <s v="27. Jun"/>
+          <s v="28. Jun"/>
+          <s v="29. Jun"/>
+          <s v="30. Jun"/>
+          <s v="01. Jul"/>
+          <s v="02. Jul"/>
+          <s v="03. Jul"/>
+          <s v="04. Jul"/>
+          <s v="05. Jul"/>
+          <s v="06. Jul"/>
+          <s v="07. Jul"/>
+          <s v="08. Jul"/>
+          <s v="09. Jul"/>
+          <s v="10. Jul"/>
+          <s v="11. Jul"/>
+          <s v="12. Jul"/>
+          <s v="13. Jul"/>
+          <s v="14. Jul"/>
+          <s v="15. Jul"/>
+          <s v="16. Jul"/>
+          <s v="17. Jul"/>
+          <s v="18. Jul"/>
+          <s v="19. Jul"/>
+          <s v="20. Jul"/>
+          <s v="21. Jul"/>
+          <s v="22. Jul"/>
+          <s v="23. Jul"/>
+          <s v="24. Jul"/>
+          <s v="25. Jul"/>
+          <s v="26. Jul"/>
+          <s v="27. Jul"/>
+          <s v="28. Jul"/>
+          <s v="29. Jul"/>
+          <s v="30. Jul"/>
+          <s v="31. Jul"/>
+          <s v="01. Aug"/>
+          <s v="02. Aug"/>
+          <s v="03. Aug"/>
+          <s v="04. Aug"/>
+          <s v="05. Aug"/>
+          <s v="06. Aug"/>
+          <s v="07. Aug"/>
+          <s v="08. Aug"/>
+          <s v="09. Aug"/>
+          <s v="10. Aug"/>
+          <s v="11. Aug"/>
+          <s v="12. Aug"/>
+          <s v="13. Aug"/>
+          <s v="14. Aug"/>
+          <s v="15. Aug"/>
+          <s v="16. Aug"/>
+          <s v="17. Aug"/>
+          <s v="18. Aug"/>
+          <s v="19. Aug"/>
+          <s v="20. Aug"/>
+          <s v="21. Aug"/>
+          <s v="22. Aug"/>
+          <s v="23. Aug"/>
+          <s v="24. Aug"/>
+          <s v="25. Aug"/>
+          <s v="26. Aug"/>
+          <s v="27. Aug"/>
+          <s v="28. Aug"/>
+          <s v="29. Aug"/>
+          <s v="30. Aug"/>
+          <s v="31. Aug"/>
+          <s v="01. Sep"/>
+          <s v="02. Sep"/>
+          <s v="03. Sep"/>
+          <s v="04. Sep"/>
+          <s v="05. Sep"/>
+          <s v="06. Sep"/>
+          <s v="07. Sep"/>
+          <s v="08. Sep"/>
+          <s v="09. Sep"/>
+          <s v="10. Sep"/>
+          <s v="11. Sep"/>
+          <s v="12. Sep"/>
+          <s v="13. Sep"/>
+          <s v="14. Sep"/>
+          <s v="15. Sep"/>
+          <s v="16. Sep"/>
+          <s v="17. Sep"/>
+          <s v="18. Sep"/>
+          <s v="19. Sep"/>
+          <s v="20. Sep"/>
+          <s v="21. Sep"/>
+          <s v="22. Sep"/>
+          <s v="23. Sep"/>
+          <s v="24. Sep"/>
+          <s v="25. Sep"/>
+          <s v="26. Sep"/>
+          <s v="27. Sep"/>
+          <s v="28. Sep"/>
+          <s v="29. Sep"/>
+          <s v="30. Sep"/>
+          <s v="01. Oct"/>
+          <s v="02. Oct"/>
+          <s v="03. Oct"/>
+          <s v="04. Oct"/>
+          <s v="05. Oct"/>
+          <s v="06. Oct"/>
+          <s v="07. Oct"/>
+          <s v="08. Oct"/>
+          <s v="09. Oct"/>
+          <s v="10. Oct"/>
+          <s v="11. Oct"/>
+          <s v="12. Oct"/>
+          <s v="13. Oct"/>
+          <s v="14. Oct"/>
+          <s v="15. Oct"/>
+          <s v="16. Oct"/>
+          <s v="17. Oct"/>
+          <s v="18. Oct"/>
+          <s v="19. Oct"/>
+          <s v="20. Oct"/>
+          <s v="21. Oct"/>
+          <s v="22. Oct"/>
+          <s v="23. Oct"/>
+          <s v="24. Oct"/>
+          <s v="25. Oct"/>
+          <s v="26. Oct"/>
+          <s v="27. Oct"/>
+          <s v="28. Oct"/>
+          <s v="29. Oct"/>
+          <s v="30. Oct"/>
+          <s v="31. Oct"/>
+          <s v="01. Nov"/>
+          <s v="02. Nov"/>
+          <s v="03. Nov"/>
+          <s v="04. Nov"/>
+          <s v="05. Nov"/>
+          <s v="06. Nov"/>
+          <s v="07. Nov"/>
+          <s v="08. Nov"/>
+          <s v="09. Nov"/>
+          <s v="10. Nov"/>
+          <s v="11. Nov"/>
+          <s v="12. Nov"/>
+          <s v="13. Nov"/>
+          <s v="14. Nov"/>
+          <s v="15. Nov"/>
+          <s v="16. Nov"/>
+          <s v="17. Nov"/>
+          <s v="18. Nov"/>
+          <s v="19. Nov"/>
+          <s v="20. Nov"/>
+          <s v="21. Nov"/>
+          <s v="22. Nov"/>
+          <s v="23. Nov"/>
+          <s v="24. Nov"/>
+          <s v="25. Nov"/>
+          <s v="26. Nov"/>
+          <s v="27. Nov"/>
+          <s v="28. Nov"/>
+          <s v="29. Nov"/>
+          <s v="30. Nov"/>
+          <s v="01. Dec"/>
+          <s v="02. Dec"/>
+          <s v="03. Dec"/>
+          <s v="04. Dec"/>
+          <s v="05. Dec"/>
+          <s v="06. Dec"/>
+          <s v="07. Dec"/>
+          <s v="08. Dec"/>
+          <s v="09. Dec"/>
+          <s v="10. Dec"/>
+          <s v="11. Dec"/>
+          <s v="12. Dec"/>
+          <s v="13. Dec"/>
+          <s v="14. Dec"/>
+          <s v="15. Dec"/>
+          <s v="16. Dec"/>
+          <s v="17. Dec"/>
+          <s v="18. Dec"/>
+          <s v="19. Dec"/>
+          <s v="20. Dec"/>
+          <s v="21. Dec"/>
+          <s v="22. Dec"/>
+          <s v="23. Dec"/>
+          <s v="24. Dec"/>
+          <s v="25. Dec"/>
+          <s v="26. Dec"/>
+          <s v="27. Dec"/>
+          <s v="28. Dec"/>
+          <s v="29. Dec"/>
+          <s v="30. Dec"/>
+          <s v="31. Dec"/>
+          <s v="&gt;02.09.17"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Months (cohort_month)" numFmtId="0" databaseField="0">
+      <fieldGroup base="0">
+        <rangePr groupBy="months" startDate="2017-01-01T00:00:00" endDate="2017-09-02T00:00:00"/>
+        <groupItems count="14">
+          <s v="&lt;01.01.17"/>
+          <s v="Jan"/>
+          <s v="Feb"/>
+          <s v="Mar"/>
+          <s v="Apr"/>
+          <s v="May"/>
+          <s v="Jun"/>
+          <s v="Jul"/>
+          <s v="Aug"/>
+          <s v="Sep"/>
+          <s v="Oct"/>
+          <s v="Nov"/>
+          <s v="Dec"/>
+          <s v="&gt;02.09.17"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="81">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="717"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="717"/>
+    <n v="2.7889999999999998E-3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="4"/>
+    <n v="717"/>
+    <n v="5.5789999999999998E-3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="5"/>
+    <n v="717"/>
+    <n v="6.9740000000000002E-3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="8"/>
+    <n v="717"/>
+    <n v="1.1158E-2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="9"/>
+    <n v="717"/>
+    <n v="1.2552000000000001E-2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="6"/>
+    <n v="12"/>
+    <n v="717"/>
+    <n v="1.6736000000000001E-2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="7"/>
+    <n v="12"/>
+    <n v="717"/>
+    <n v="1.6736000000000001E-2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="8"/>
+    <n v="13"/>
+    <n v="717"/>
+    <n v="1.8131000000000001E-2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="1628"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="1628"/>
+    <n v="1.843E-3"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="8"/>
+    <n v="1628"/>
+    <n v="4.914E-3"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <n v="10"/>
+    <n v="1628"/>
+    <n v="6.143E-3"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <n v="17"/>
+    <n v="1628"/>
+    <n v="1.0442E-2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <n v="19"/>
+    <n v="1628"/>
+    <n v="1.1671000000000001E-2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="6"/>
+    <n v="23"/>
+    <n v="1628"/>
+    <n v="1.4128E-2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="7"/>
+    <n v="25"/>
+    <n v="1628"/>
+    <n v="1.5356E-2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="8"/>
+    <n v="27"/>
+    <n v="1628"/>
+    <n v="1.6584999999999999E-2"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="2503"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="11"/>
+    <n v="2503"/>
+    <n v="4.3949999999999996E-3"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="20"/>
+    <n v="2503"/>
+    <n v="7.9900000000000006E-3"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="3"/>
+    <n v="29"/>
+    <n v="2503"/>
+    <n v="1.1586000000000001E-2"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="4"/>
+    <n v="37"/>
+    <n v="2503"/>
+    <n v="1.4782E-2"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="5"/>
+    <n v="40"/>
+    <n v="2503"/>
+    <n v="1.5980999999999999E-2"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="6"/>
+    <n v="44"/>
+    <n v="2503"/>
+    <n v="1.7579000000000001E-2"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="7"/>
+    <n v="52"/>
+    <n v="2503"/>
+    <n v="2.0774999999999998E-2"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="8"/>
+    <n v="59"/>
+    <n v="2503"/>
+    <n v="2.3571999999999999E-2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="2256"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="14"/>
+    <n v="2256"/>
+    <n v="6.2059999999999997E-3"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="19"/>
+    <n v="2256"/>
+    <n v="8.4220000000000007E-3"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="23"/>
+    <n v="2256"/>
+    <n v="1.0194999999999999E-2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="4"/>
+    <n v="29"/>
+    <n v="2256"/>
+    <n v="1.2855E-2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="5"/>
+    <n v="35"/>
+    <n v="2256"/>
+    <n v="1.5514E-2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="6"/>
+    <n v="42"/>
+    <n v="2256"/>
+    <n v="1.8617000000000002E-2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="7"/>
+    <n v="49"/>
+    <n v="2256"/>
+    <n v="2.172E-2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="8"/>
+    <n v="56"/>
+    <n v="2256"/>
+    <n v="2.4823000000000001E-2"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="3451"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="16"/>
+    <n v="3451"/>
+    <n v="4.6360000000000004E-3"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="2"/>
+    <n v="32"/>
+    <n v="3451"/>
+    <n v="9.273E-3"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="3"/>
+    <n v="40"/>
+    <n v="3451"/>
+    <n v="1.1591000000000001E-2"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="4"/>
+    <n v="49"/>
+    <n v="3451"/>
+    <n v="1.4199E-2"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="5"/>
+    <n v="57"/>
+    <n v="3451"/>
+    <n v="1.6517E-2"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="6"/>
+    <n v="69"/>
+    <n v="3451"/>
+    <n v="1.9994000000000001E-2"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="7"/>
+    <n v="74"/>
+    <n v="3451"/>
+    <n v="2.1443E-2"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="8"/>
+    <n v="81"/>
+    <n v="3451"/>
+    <n v="2.3470999999999999E-2"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="3037"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="15"/>
+    <n v="3037"/>
+    <n v="4.9389999999999998E-3"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="2"/>
+    <n v="26"/>
+    <n v="3037"/>
+    <n v="8.5609999999999992E-3"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="3"/>
+    <n v="37"/>
+    <n v="3037"/>
+    <n v="1.2182999999999999E-2"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="4"/>
+    <n v="43"/>
+    <n v="3037"/>
+    <n v="1.4159E-2"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="5"/>
+    <n v="53"/>
+    <n v="3037"/>
+    <n v="1.7451000000000001E-2"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="6"/>
+    <n v="63"/>
+    <n v="3037"/>
+    <n v="2.0743999999999999E-2"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="7"/>
+    <n v="70"/>
+    <n v="3037"/>
+    <n v="2.3049E-2"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="8"/>
+    <n v="74"/>
+    <n v="3037"/>
+    <n v="2.4365999999999999E-2"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="3752"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="1"/>
+    <n v="20"/>
+    <n v="3752"/>
+    <n v="5.3299999999999997E-3"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="2"/>
+    <n v="32"/>
+    <n v="3752"/>
+    <n v="8.5290000000000001E-3"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="3"/>
+    <n v="40"/>
+    <n v="3752"/>
+    <n v="1.0661E-2"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="4"/>
+    <n v="50"/>
+    <n v="3752"/>
+    <n v="1.3325999999999999E-2"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="5"/>
+    <n v="58"/>
+    <n v="3752"/>
+    <n v="1.5458E-2"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="6"/>
+    <n v="70"/>
+    <n v="3752"/>
+    <n v="1.8657E-2"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="7"/>
+    <n v="74"/>
+    <n v="3752"/>
+    <n v="1.9723000000000001E-2"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="8"/>
+    <n v="81"/>
+    <n v="3752"/>
+    <n v="2.1588E-2"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="4057"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="1"/>
+    <n v="28"/>
+    <n v="4057"/>
+    <n v="6.9020000000000001E-3"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="2"/>
+    <n v="41"/>
+    <n v="4057"/>
+    <n v="1.0106E-2"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="3"/>
+    <n v="50"/>
+    <n v="4057"/>
+    <n v="1.2324E-2"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="4"/>
+    <n v="64"/>
+    <n v="4057"/>
+    <n v="1.5775000000000001E-2"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="5"/>
+    <n v="82"/>
+    <n v="4057"/>
+    <n v="2.0212000000000001E-2"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="6"/>
+    <n v="93"/>
+    <n v="4057"/>
+    <n v="2.2922999999999999E-2"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="7"/>
+    <n v="101"/>
+    <n v="4057"/>
+    <n v="2.4895E-2"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="8"/>
+    <n v="105"/>
+    <n v="4057"/>
+    <n v="2.5881000000000001E-2"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="4004"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="1"/>
+    <n v="28"/>
+    <n v="4004"/>
+    <n v="6.9930000000000001E-3"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="2"/>
+    <n v="48"/>
+    <n v="4004"/>
+    <n v="1.1988E-2"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="3"/>
+    <n v="58"/>
+    <n v="4004"/>
+    <n v="1.4486000000000001E-2"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="4"/>
+    <n v="73"/>
+    <n v="4004"/>
+    <n v="1.8232000000000002E-2"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="5"/>
+    <n v="81"/>
+    <n v="4004"/>
+    <n v="2.0230000000000001E-2"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="6"/>
+    <n v="87"/>
+    <n v="4004"/>
+    <n v="2.1728000000000001E-2"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="7"/>
+    <n v="94"/>
+    <n v="4004"/>
+    <n v="2.3477000000000001E-2"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="8"/>
+    <n v="104"/>
+    <n v="4004"/>
+    <n v="2.5974000000000001E-2"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C1D023F3-F212-0B40-B73F-A834285F84A9}" name="PivotTable2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9" rowHeaderCaption="Months since first purchase" colHeaderCaption="Cohort Months">
+  <location ref="G14:P24" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField axis="axisCol" numFmtId="14" showAll="0">
+      <items count="10">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="10">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="369">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="25"/>
+        <item sd="0" x="26"/>
+        <item sd="0" x="27"/>
+        <item sd="0" x="28"/>
+        <item sd="0" x="29"/>
+        <item sd="0" x="30"/>
+        <item sd="0" x="31"/>
+        <item sd="0" x="32"/>
+        <item sd="0" x="33"/>
+        <item sd="0" x="34"/>
+        <item sd="0" x="35"/>
+        <item sd="0" x="36"/>
+        <item sd="0" x="37"/>
+        <item sd="0" x="38"/>
+        <item sd="0" x="39"/>
+        <item sd="0" x="40"/>
+        <item sd="0" x="41"/>
+        <item sd="0" x="42"/>
+        <item sd="0" x="43"/>
+        <item sd="0" x="44"/>
+        <item sd="0" x="45"/>
+        <item sd="0" x="46"/>
+        <item sd="0" x="47"/>
+        <item sd="0" x="48"/>
+        <item sd="0" x="49"/>
+        <item sd="0" x="50"/>
+        <item sd="0" x="51"/>
+        <item sd="0" x="52"/>
+        <item sd="0" x="53"/>
+        <item sd="0" x="54"/>
+        <item sd="0" x="55"/>
+        <item sd="0" x="56"/>
+        <item sd="0" x="57"/>
+        <item sd="0" x="58"/>
+        <item sd="0" x="59"/>
+        <item sd="0" x="60"/>
+        <item sd="0" x="61"/>
+        <item sd="0" x="62"/>
+        <item sd="0" x="63"/>
+        <item sd="0" x="64"/>
+        <item sd="0" x="65"/>
+        <item sd="0" x="66"/>
+        <item sd="0" x="67"/>
+        <item sd="0" x="68"/>
+        <item sd="0" x="69"/>
+        <item sd="0" x="70"/>
+        <item sd="0" x="71"/>
+        <item sd="0" x="72"/>
+        <item sd="0" x="73"/>
+        <item sd="0" x="74"/>
+        <item sd="0" x="75"/>
+        <item sd="0" x="76"/>
+        <item sd="0" x="77"/>
+        <item sd="0" x="78"/>
+        <item sd="0" x="79"/>
+        <item sd="0" x="80"/>
+        <item sd="0" x="81"/>
+        <item sd="0" x="82"/>
+        <item sd="0" x="83"/>
+        <item sd="0" x="84"/>
+        <item sd="0" x="85"/>
+        <item sd="0" x="86"/>
+        <item sd="0" x="87"/>
+        <item sd="0" x="88"/>
+        <item sd="0" x="89"/>
+        <item sd="0" x="90"/>
+        <item sd="0" x="91"/>
+        <item sd="0" x="92"/>
+        <item sd="0" x="93"/>
+        <item sd="0" x="94"/>
+        <item sd="0" x="95"/>
+        <item sd="0" x="96"/>
+        <item sd="0" x="97"/>
+        <item sd="0" x="98"/>
+        <item sd="0" x="99"/>
+        <item sd="0" x="100"/>
+        <item sd="0" x="101"/>
+        <item sd="0" x="102"/>
+        <item sd="0" x="103"/>
+        <item sd="0" x="104"/>
+        <item sd="0" x="105"/>
+        <item sd="0" x="106"/>
+        <item sd="0" x="107"/>
+        <item sd="0" x="108"/>
+        <item sd="0" x="109"/>
+        <item sd="0" x="110"/>
+        <item sd="0" x="111"/>
+        <item sd="0" x="112"/>
+        <item sd="0" x="113"/>
+        <item sd="0" x="114"/>
+        <item sd="0" x="115"/>
+        <item sd="0" x="116"/>
+        <item sd="0" x="117"/>
+        <item sd="0" x="118"/>
+        <item sd="0" x="119"/>
+        <item sd="0" x="120"/>
+        <item sd="0" x="121"/>
+        <item sd="0" x="122"/>
+        <item sd="0" x="123"/>
+        <item sd="0" x="124"/>
+        <item sd="0" x="125"/>
+        <item sd="0" x="126"/>
+        <item sd="0" x="127"/>
+        <item sd="0" x="128"/>
+        <item sd="0" x="129"/>
+        <item sd="0" x="130"/>
+        <item sd="0" x="131"/>
+        <item sd="0" x="132"/>
+        <item sd="0" x="133"/>
+        <item sd="0" x="134"/>
+        <item sd="0" x="135"/>
+        <item sd="0" x="136"/>
+        <item sd="0" x="137"/>
+        <item sd="0" x="138"/>
+        <item sd="0" x="139"/>
+        <item sd="0" x="140"/>
+        <item sd="0" x="141"/>
+        <item sd="0" x="142"/>
+        <item sd="0" x="143"/>
+        <item sd="0" x="144"/>
+        <item sd="0" x="145"/>
+        <item sd="0" x="146"/>
+        <item sd="0" x="147"/>
+        <item sd="0" x="148"/>
+        <item sd="0" x="149"/>
+        <item sd="0" x="150"/>
+        <item sd="0" x="151"/>
+        <item sd="0" x="152"/>
+        <item sd="0" x="153"/>
+        <item sd="0" x="154"/>
+        <item sd="0" x="155"/>
+        <item sd="0" x="156"/>
+        <item sd="0" x="157"/>
+        <item sd="0" x="158"/>
+        <item sd="0" x="159"/>
+        <item sd="0" x="160"/>
+        <item sd="0" x="161"/>
+        <item sd="0" x="162"/>
+        <item sd="0" x="163"/>
+        <item sd="0" x="164"/>
+        <item sd="0" x="165"/>
+        <item sd="0" x="166"/>
+        <item sd="0" x="167"/>
+        <item sd="0" x="168"/>
+        <item sd="0" x="169"/>
+        <item sd="0" x="170"/>
+        <item sd="0" x="171"/>
+        <item sd="0" x="172"/>
+        <item sd="0" x="173"/>
+        <item sd="0" x="174"/>
+        <item sd="0" x="175"/>
+        <item sd="0" x="176"/>
+        <item sd="0" x="177"/>
+        <item sd="0" x="178"/>
+        <item sd="0" x="179"/>
+        <item sd="0" x="180"/>
+        <item sd="0" x="181"/>
+        <item sd="0" x="182"/>
+        <item sd="0" x="183"/>
+        <item sd="0" x="184"/>
+        <item sd="0" x="185"/>
+        <item sd="0" x="186"/>
+        <item sd="0" x="187"/>
+        <item sd="0" x="188"/>
+        <item sd="0" x="189"/>
+        <item sd="0" x="190"/>
+        <item sd="0" x="191"/>
+        <item sd="0" x="192"/>
+        <item sd="0" x="193"/>
+        <item sd="0" x="194"/>
+        <item sd="0" x="195"/>
+        <item sd="0" x="196"/>
+        <item sd="0" x="197"/>
+        <item sd="0" x="198"/>
+        <item sd="0" x="199"/>
+        <item sd="0" x="200"/>
+        <item sd="0" x="201"/>
+        <item sd="0" x="202"/>
+        <item sd="0" x="203"/>
+        <item sd="0" x="204"/>
+        <item sd="0" x="205"/>
+        <item sd="0" x="206"/>
+        <item sd="0" x="207"/>
+        <item sd="0" x="208"/>
+        <item sd="0" x="209"/>
+        <item sd="0" x="210"/>
+        <item sd="0" x="211"/>
+        <item sd="0" x="212"/>
+        <item sd="0" x="213"/>
+        <item sd="0" x="214"/>
+        <item sd="0" x="215"/>
+        <item sd="0" x="216"/>
+        <item sd="0" x="217"/>
+        <item sd="0" x="218"/>
+        <item sd="0" x="219"/>
+        <item sd="0" x="220"/>
+        <item sd="0" x="221"/>
+        <item sd="0" x="222"/>
+        <item sd="0" x="223"/>
+        <item sd="0" x="224"/>
+        <item sd="0" x="225"/>
+        <item sd="0" x="226"/>
+        <item sd="0" x="227"/>
+        <item sd="0" x="228"/>
+        <item sd="0" x="229"/>
+        <item sd="0" x="230"/>
+        <item sd="0" x="231"/>
+        <item sd="0" x="232"/>
+        <item sd="0" x="233"/>
+        <item sd="0" x="234"/>
+        <item sd="0" x="235"/>
+        <item sd="0" x="236"/>
+        <item sd="0" x="237"/>
+        <item sd="0" x="238"/>
+        <item sd="0" x="239"/>
+        <item sd="0" x="240"/>
+        <item sd="0" x="241"/>
+        <item sd="0" x="242"/>
+        <item sd="0" x="243"/>
+        <item sd="0" x="244"/>
+        <item sd="0" x="245"/>
+        <item sd="0" x="246"/>
+        <item sd="0" x="247"/>
+        <item sd="0" x="248"/>
+        <item sd="0" x="249"/>
+        <item sd="0" x="250"/>
+        <item sd="0" x="251"/>
+        <item sd="0" x="252"/>
+        <item sd="0" x="253"/>
+        <item sd="0" x="254"/>
+        <item sd="0" x="255"/>
+        <item sd="0" x="256"/>
+        <item sd="0" x="257"/>
+        <item sd="0" x="258"/>
+        <item sd="0" x="259"/>
+        <item sd="0" x="260"/>
+        <item sd="0" x="261"/>
+        <item sd="0" x="262"/>
+        <item sd="0" x="263"/>
+        <item sd="0" x="264"/>
+        <item sd="0" x="265"/>
+        <item sd="0" x="266"/>
+        <item sd="0" x="267"/>
+        <item sd="0" x="268"/>
+        <item sd="0" x="269"/>
+        <item sd="0" x="270"/>
+        <item sd="0" x="271"/>
+        <item sd="0" x="272"/>
+        <item sd="0" x="273"/>
+        <item sd="0" x="274"/>
+        <item sd="0" x="275"/>
+        <item sd="0" x="276"/>
+        <item sd="0" x="277"/>
+        <item sd="0" x="278"/>
+        <item sd="0" x="279"/>
+        <item sd="0" x="280"/>
+        <item sd="0" x="281"/>
+        <item sd="0" x="282"/>
+        <item sd="0" x="283"/>
+        <item sd="0" x="284"/>
+        <item sd="0" x="285"/>
+        <item sd="0" x="286"/>
+        <item sd="0" x="287"/>
+        <item sd="0" x="288"/>
+        <item sd="0" x="289"/>
+        <item sd="0" x="290"/>
+        <item sd="0" x="291"/>
+        <item sd="0" x="292"/>
+        <item sd="0" x="293"/>
+        <item sd="0" x="294"/>
+        <item sd="0" x="295"/>
+        <item sd="0" x="296"/>
+        <item sd="0" x="297"/>
+        <item sd="0" x="298"/>
+        <item sd="0" x="299"/>
+        <item sd="0" x="300"/>
+        <item sd="0" x="301"/>
+        <item sd="0" x="302"/>
+        <item sd="0" x="303"/>
+        <item sd="0" x="304"/>
+        <item sd="0" x="305"/>
+        <item sd="0" x="306"/>
+        <item sd="0" x="307"/>
+        <item sd="0" x="308"/>
+        <item sd="0" x="309"/>
+        <item sd="0" x="310"/>
+        <item sd="0" x="311"/>
+        <item sd="0" x="312"/>
+        <item sd="0" x="313"/>
+        <item sd="0" x="314"/>
+        <item sd="0" x="315"/>
+        <item sd="0" x="316"/>
+        <item sd="0" x="317"/>
+        <item sd="0" x="318"/>
+        <item sd="0" x="319"/>
+        <item sd="0" x="320"/>
+        <item sd="0" x="321"/>
+        <item sd="0" x="322"/>
+        <item sd="0" x="323"/>
+        <item sd="0" x="324"/>
+        <item sd="0" x="325"/>
+        <item sd="0" x="326"/>
+        <item sd="0" x="327"/>
+        <item sd="0" x="328"/>
+        <item sd="0" x="329"/>
+        <item sd="0" x="330"/>
+        <item sd="0" x="331"/>
+        <item sd="0" x="332"/>
+        <item sd="0" x="333"/>
+        <item sd="0" x="334"/>
+        <item sd="0" x="335"/>
+        <item sd="0" x="336"/>
+        <item sd="0" x="337"/>
+        <item sd="0" x="338"/>
+        <item sd="0" x="339"/>
+        <item sd="0" x="340"/>
+        <item sd="0" x="341"/>
+        <item sd="0" x="342"/>
+        <item sd="0" x="343"/>
+        <item sd="0" x="344"/>
+        <item sd="0" x="345"/>
+        <item sd="0" x="346"/>
+        <item sd="0" x="347"/>
+        <item sd="0" x="348"/>
+        <item sd="0" x="349"/>
+        <item sd="0" x="350"/>
+        <item sd="0" x="351"/>
+        <item sd="0" x="352"/>
+        <item sd="0" x="353"/>
+        <item sd="0" x="354"/>
+        <item sd="0" x="355"/>
+        <item sd="0" x="356"/>
+        <item sd="0" x="357"/>
+        <item sd="0" x="358"/>
+        <item sd="0" x="359"/>
+        <item sd="0" x="360"/>
+        <item sd="0" x="361"/>
+        <item sd="0" x="362"/>
+        <item sd="0" x="363"/>
+        <item sd="0" x="364"/>
+        <item sd="0" x="365"/>
+        <item sd="0" x="366"/>
+        <item sd="0" x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="9">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="9">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of cumulative_retention" fld="4" subtotal="average" baseField="0" baseItem="0" numFmtId="10"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="7">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="8">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <conditionalFormats count="1">
+    <conditionalFormat priority="2">
+      <pivotAreas count="1">
+        <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="1" count="8" selected="0">
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+  </conditionalFormats>
+  <chartFormats count="45">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="11" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="12" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="13" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="14" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="15" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="16" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="17" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="18" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="19" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="20" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="21" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="22" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="23" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="24" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="25" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="26" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="27" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="28" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="29" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="30" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="31" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="32" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="33" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="34" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="35" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7078B821-F574-0441-82CE-19F697AAA684}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8" rowHeaderCaption="Cohort Months" colHeaderCaption="Months since first purchase">
+  <location ref="G1:P11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField axis="axisRow" numFmtId="14" showAll="0">
+      <items count="10">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="10">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="369">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="25"/>
+        <item sd="0" x="26"/>
+        <item sd="0" x="27"/>
+        <item sd="0" x="28"/>
+        <item sd="0" x="29"/>
+        <item sd="0" x="30"/>
+        <item sd="0" x="31"/>
+        <item sd="0" x="32"/>
+        <item sd="0" x="33"/>
+        <item sd="0" x="34"/>
+        <item sd="0" x="35"/>
+        <item sd="0" x="36"/>
+        <item sd="0" x="37"/>
+        <item sd="0" x="38"/>
+        <item sd="0" x="39"/>
+        <item sd="0" x="40"/>
+        <item sd="0" x="41"/>
+        <item sd="0" x="42"/>
+        <item sd="0" x="43"/>
+        <item sd="0" x="44"/>
+        <item sd="0" x="45"/>
+        <item sd="0" x="46"/>
+        <item sd="0" x="47"/>
+        <item sd="0" x="48"/>
+        <item sd="0" x="49"/>
+        <item sd="0" x="50"/>
+        <item sd="0" x="51"/>
+        <item sd="0" x="52"/>
+        <item sd="0" x="53"/>
+        <item sd="0" x="54"/>
+        <item sd="0" x="55"/>
+        <item sd="0" x="56"/>
+        <item sd="0" x="57"/>
+        <item sd="0" x="58"/>
+        <item sd="0" x="59"/>
+        <item sd="0" x="60"/>
+        <item sd="0" x="61"/>
+        <item sd="0" x="62"/>
+        <item sd="0" x="63"/>
+        <item sd="0" x="64"/>
+        <item sd="0" x="65"/>
+        <item sd="0" x="66"/>
+        <item sd="0" x="67"/>
+        <item sd="0" x="68"/>
+        <item sd="0" x="69"/>
+        <item sd="0" x="70"/>
+        <item sd="0" x="71"/>
+        <item sd="0" x="72"/>
+        <item sd="0" x="73"/>
+        <item sd="0" x="74"/>
+        <item sd="0" x="75"/>
+        <item sd="0" x="76"/>
+        <item sd="0" x="77"/>
+        <item sd="0" x="78"/>
+        <item sd="0" x="79"/>
+        <item sd="0" x="80"/>
+        <item sd="0" x="81"/>
+        <item sd="0" x="82"/>
+        <item sd="0" x="83"/>
+        <item sd="0" x="84"/>
+        <item sd="0" x="85"/>
+        <item sd="0" x="86"/>
+        <item sd="0" x="87"/>
+        <item sd="0" x="88"/>
+        <item sd="0" x="89"/>
+        <item sd="0" x="90"/>
+        <item sd="0" x="91"/>
+        <item sd="0" x="92"/>
+        <item sd="0" x="93"/>
+        <item sd="0" x="94"/>
+        <item sd="0" x="95"/>
+        <item sd="0" x="96"/>
+        <item sd="0" x="97"/>
+        <item sd="0" x="98"/>
+        <item sd="0" x="99"/>
+        <item sd="0" x="100"/>
+        <item sd="0" x="101"/>
+        <item sd="0" x="102"/>
+        <item sd="0" x="103"/>
+        <item sd="0" x="104"/>
+        <item sd="0" x="105"/>
+        <item sd="0" x="106"/>
+        <item sd="0" x="107"/>
+        <item sd="0" x="108"/>
+        <item sd="0" x="109"/>
+        <item sd="0" x="110"/>
+        <item sd="0" x="111"/>
+        <item sd="0" x="112"/>
+        <item sd="0" x="113"/>
+        <item sd="0" x="114"/>
+        <item sd="0" x="115"/>
+        <item sd="0" x="116"/>
+        <item sd="0" x="117"/>
+        <item sd="0" x="118"/>
+        <item sd="0" x="119"/>
+        <item sd="0" x="120"/>
+        <item sd="0" x="121"/>
+        <item sd="0" x="122"/>
+        <item sd="0" x="123"/>
+        <item sd="0" x="124"/>
+        <item sd="0" x="125"/>
+        <item sd="0" x="126"/>
+        <item sd="0" x="127"/>
+        <item sd="0" x="128"/>
+        <item sd="0" x="129"/>
+        <item sd="0" x="130"/>
+        <item sd="0" x="131"/>
+        <item sd="0" x="132"/>
+        <item sd="0" x="133"/>
+        <item sd="0" x="134"/>
+        <item sd="0" x="135"/>
+        <item sd="0" x="136"/>
+        <item sd="0" x="137"/>
+        <item sd="0" x="138"/>
+        <item sd="0" x="139"/>
+        <item sd="0" x="140"/>
+        <item sd="0" x="141"/>
+        <item sd="0" x="142"/>
+        <item sd="0" x="143"/>
+        <item sd="0" x="144"/>
+        <item sd="0" x="145"/>
+        <item sd="0" x="146"/>
+        <item sd="0" x="147"/>
+        <item sd="0" x="148"/>
+        <item sd="0" x="149"/>
+        <item sd="0" x="150"/>
+        <item sd="0" x="151"/>
+        <item sd="0" x="152"/>
+        <item sd="0" x="153"/>
+        <item sd="0" x="154"/>
+        <item sd="0" x="155"/>
+        <item sd="0" x="156"/>
+        <item sd="0" x="157"/>
+        <item sd="0" x="158"/>
+        <item sd="0" x="159"/>
+        <item sd="0" x="160"/>
+        <item sd="0" x="161"/>
+        <item sd="0" x="162"/>
+        <item sd="0" x="163"/>
+        <item sd="0" x="164"/>
+        <item sd="0" x="165"/>
+        <item sd="0" x="166"/>
+        <item sd="0" x="167"/>
+        <item sd="0" x="168"/>
+        <item sd="0" x="169"/>
+        <item sd="0" x="170"/>
+        <item sd="0" x="171"/>
+        <item sd="0" x="172"/>
+        <item sd="0" x="173"/>
+        <item sd="0" x="174"/>
+        <item sd="0" x="175"/>
+        <item sd="0" x="176"/>
+        <item sd="0" x="177"/>
+        <item sd="0" x="178"/>
+        <item sd="0" x="179"/>
+        <item sd="0" x="180"/>
+        <item sd="0" x="181"/>
+        <item sd="0" x="182"/>
+        <item sd="0" x="183"/>
+        <item sd="0" x="184"/>
+        <item sd="0" x="185"/>
+        <item sd="0" x="186"/>
+        <item sd="0" x="187"/>
+        <item sd="0" x="188"/>
+        <item sd="0" x="189"/>
+        <item sd="0" x="190"/>
+        <item sd="0" x="191"/>
+        <item sd="0" x="192"/>
+        <item sd="0" x="193"/>
+        <item sd="0" x="194"/>
+        <item sd="0" x="195"/>
+        <item sd="0" x="196"/>
+        <item sd="0" x="197"/>
+        <item sd="0" x="198"/>
+        <item sd="0" x="199"/>
+        <item sd="0" x="200"/>
+        <item sd="0" x="201"/>
+        <item sd="0" x="202"/>
+        <item sd="0" x="203"/>
+        <item sd="0" x="204"/>
+        <item sd="0" x="205"/>
+        <item sd="0" x="206"/>
+        <item sd="0" x="207"/>
+        <item sd="0" x="208"/>
+        <item sd="0" x="209"/>
+        <item sd="0" x="210"/>
+        <item sd="0" x="211"/>
+        <item sd="0" x="212"/>
+        <item sd="0" x="213"/>
+        <item sd="0" x="214"/>
+        <item sd="0" x="215"/>
+        <item sd="0" x="216"/>
+        <item sd="0" x="217"/>
+        <item sd="0" x="218"/>
+        <item sd="0" x="219"/>
+        <item sd="0" x="220"/>
+        <item sd="0" x="221"/>
+        <item sd="0" x="222"/>
+        <item sd="0" x="223"/>
+        <item sd="0" x="224"/>
+        <item sd="0" x="225"/>
+        <item sd="0" x="226"/>
+        <item sd="0" x="227"/>
+        <item sd="0" x="228"/>
+        <item sd="0" x="229"/>
+        <item sd="0" x="230"/>
+        <item sd="0" x="231"/>
+        <item sd="0" x="232"/>
+        <item sd="0" x="233"/>
+        <item sd="0" x="234"/>
+        <item sd="0" x="235"/>
+        <item sd="0" x="236"/>
+        <item sd="0" x="237"/>
+        <item sd="0" x="238"/>
+        <item sd="0" x="239"/>
+        <item sd="0" x="240"/>
+        <item sd="0" x="241"/>
+        <item sd="0" x="242"/>
+        <item sd="0" x="243"/>
+        <item sd="0" x="244"/>
+        <item sd="0" x="245"/>
+        <item sd="0" x="246"/>
+        <item sd="0" x="247"/>
+        <item sd="0" x="248"/>
+        <item sd="0" x="249"/>
+        <item sd="0" x="250"/>
+        <item sd="0" x="251"/>
+        <item sd="0" x="252"/>
+        <item sd="0" x="253"/>
+        <item sd="0" x="254"/>
+        <item sd="0" x="255"/>
+        <item sd="0" x="256"/>
+        <item sd="0" x="257"/>
+        <item sd="0" x="258"/>
+        <item sd="0" x="259"/>
+        <item sd="0" x="260"/>
+        <item sd="0" x="261"/>
+        <item sd="0" x="262"/>
+        <item sd="0" x="263"/>
+        <item sd="0" x="264"/>
+        <item sd="0" x="265"/>
+        <item sd="0" x="266"/>
+        <item sd="0" x="267"/>
+        <item sd="0" x="268"/>
+        <item sd="0" x="269"/>
+        <item sd="0" x="270"/>
+        <item sd="0" x="271"/>
+        <item sd="0" x="272"/>
+        <item sd="0" x="273"/>
+        <item sd="0" x="274"/>
+        <item sd="0" x="275"/>
+        <item sd="0" x="276"/>
+        <item sd="0" x="277"/>
+        <item sd="0" x="278"/>
+        <item sd="0" x="279"/>
+        <item sd="0" x="280"/>
+        <item sd="0" x="281"/>
+        <item sd="0" x="282"/>
+        <item sd="0" x="283"/>
+        <item sd="0" x="284"/>
+        <item sd="0" x="285"/>
+        <item sd="0" x="286"/>
+        <item sd="0" x="287"/>
+        <item sd="0" x="288"/>
+        <item sd="0" x="289"/>
+        <item sd="0" x="290"/>
+        <item sd="0" x="291"/>
+        <item sd="0" x="292"/>
+        <item sd="0" x="293"/>
+        <item sd="0" x="294"/>
+        <item sd="0" x="295"/>
+        <item sd="0" x="296"/>
+        <item sd="0" x="297"/>
+        <item sd="0" x="298"/>
+        <item sd="0" x="299"/>
+        <item sd="0" x="300"/>
+        <item sd="0" x="301"/>
+        <item sd="0" x="302"/>
+        <item sd="0" x="303"/>
+        <item sd="0" x="304"/>
+        <item sd="0" x="305"/>
+        <item sd="0" x="306"/>
+        <item sd="0" x="307"/>
+        <item sd="0" x="308"/>
+        <item sd="0" x="309"/>
+        <item sd="0" x="310"/>
+        <item sd="0" x="311"/>
+        <item sd="0" x="312"/>
+        <item sd="0" x="313"/>
+        <item sd="0" x="314"/>
+        <item sd="0" x="315"/>
+        <item sd="0" x="316"/>
+        <item sd="0" x="317"/>
+        <item sd="0" x="318"/>
+        <item sd="0" x="319"/>
+        <item sd="0" x="320"/>
+        <item sd="0" x="321"/>
+        <item sd="0" x="322"/>
+        <item sd="0" x="323"/>
+        <item sd="0" x="324"/>
+        <item sd="0" x="325"/>
+        <item sd="0" x="326"/>
+        <item sd="0" x="327"/>
+        <item sd="0" x="328"/>
+        <item sd="0" x="329"/>
+        <item sd="0" x="330"/>
+        <item sd="0" x="331"/>
+        <item sd="0" x="332"/>
+        <item sd="0" x="333"/>
+        <item sd="0" x="334"/>
+        <item sd="0" x="335"/>
+        <item sd="0" x="336"/>
+        <item sd="0" x="337"/>
+        <item sd="0" x="338"/>
+        <item sd="0" x="339"/>
+        <item sd="0" x="340"/>
+        <item sd="0" x="341"/>
+        <item sd="0" x="342"/>
+        <item sd="0" x="343"/>
+        <item sd="0" x="344"/>
+        <item sd="0" x="345"/>
+        <item sd="0" x="346"/>
+        <item sd="0" x="347"/>
+        <item sd="0" x="348"/>
+        <item sd="0" x="349"/>
+        <item sd="0" x="350"/>
+        <item sd="0" x="351"/>
+        <item sd="0" x="352"/>
+        <item sd="0" x="353"/>
+        <item sd="0" x="354"/>
+        <item sd="0" x="355"/>
+        <item sd="0" x="356"/>
+        <item sd="0" x="357"/>
+        <item sd="0" x="358"/>
+        <item sd="0" x="359"/>
+        <item sd="0" x="360"/>
+        <item sd="0" x="361"/>
+        <item sd="0" x="362"/>
+        <item sd="0" x="363"/>
+        <item sd="0" x="364"/>
+        <item sd="0" x="365"/>
+        <item sd="0" x="366"/>
+        <item sd="0" x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="9">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="9">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of cumulative_retention" fld="4" subtotal="average" baseField="0" baseItem="0" numFmtId="10"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="0">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <conditionalFormats count="1">
+    <conditionalFormat priority="1">
+      <pivotAreas count="1">
+        <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="1" count="8" selected="0">
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+  </conditionalFormats>
+  <chartFormats count="9">
+    <chartFormat chart="0" format="18" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="19" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="20" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="21" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="22" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="23" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="24" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="25" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="26" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -187,7 +5570,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5D8B2D7E-3A09-F34B-8E14-387B73E54CA6}" name="cumulative_retention_final_" displayName="cumulative_retention_final_" ref="A1:E82" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:E82" xr:uid="{5D8B2D7E-3A09-F34B-8E14-387B73E54CA6}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{C0EF3E19-140F-3E48-8B2E-B6F9D51D6A26}" uniqueName="1" name="cohort_month" queryTableFieldId="1" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{C0EF3E19-140F-3E48-8B2E-B6F9D51D6A26}" uniqueName="1" name="cohort_month" queryTableFieldId="1" dataDxfId="13"/>
     <tableColumn id="2" xr3:uid="{D17BAC78-3BE7-6240-B037-B507DC03F334}" uniqueName="2" name="month_number" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{A96AC37A-5FC5-1C42-8DA4-B87D0B7D84BC}" uniqueName="3" name="cumulative_count" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{6BF6A42F-8D33-C045-B828-6B895347D48C}" uniqueName="4" name="cohort_size" queryTableFieldId="4"/>
@@ -514,7 +5897,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6A8BCE-CF3E-164E-A64D-5FD5C3062789}">
-  <dimension ref="A1:E82"/>
+  <dimension ref="A1:P82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.1640625" bestFit="1" customWidth="1"/>
@@ -522,9 +5905,13 @@
     <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="16" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -540,8 +5927,14 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>42736</v>
       </c>
@@ -557,8 +5950,38 @@
       <c r="E2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
+      </c>
+      <c r="N2">
+        <v>6</v>
+      </c>
+      <c r="O2">
+        <v>7</v>
+      </c>
+      <c r="P2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>42736</v>
       </c>
@@ -574,8 +5997,38 @@
       <c r="E3">
         <v>2.7889999999999998E-3</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G3" s="3">
+        <v>42736</v>
+      </c>
+      <c r="H3" s="6">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>2.7889999999999998E-3</v>
+      </c>
+      <c r="J3" s="5">
+        <v>5.5789999999999998E-3</v>
+      </c>
+      <c r="K3" s="5">
+        <v>6.9740000000000002E-3</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1.1158E-2</v>
+      </c>
+      <c r="M3" s="5">
+        <v>1.2552000000000001E-2</v>
+      </c>
+      <c r="N3" s="5">
+        <v>1.6736000000000001E-2</v>
+      </c>
+      <c r="O3" s="5">
+        <v>1.6736000000000001E-2</v>
+      </c>
+      <c r="P3" s="5">
+        <v>1.8131000000000001E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>42736</v>
       </c>
@@ -591,8 +6044,38 @@
       <c r="E4">
         <v>5.5789999999999998E-3</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G4" s="3">
+        <v>42767</v>
+      </c>
+      <c r="H4" s="6">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1.843E-3</v>
+      </c>
+      <c r="J4" s="5">
+        <v>4.914E-3</v>
+      </c>
+      <c r="K4" s="5">
+        <v>6.143E-3</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1.0442E-2</v>
+      </c>
+      <c r="M4" s="5">
+        <v>1.1671000000000001E-2</v>
+      </c>
+      <c r="N4" s="5">
+        <v>1.4128E-2</v>
+      </c>
+      <c r="O4" s="5">
+        <v>1.5356E-2</v>
+      </c>
+      <c r="P4" s="5">
+        <v>1.6584999999999999E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>42736</v>
       </c>
@@ -608,8 +6091,38 @@
       <c r="E5">
         <v>6.9740000000000002E-3</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G5" s="3">
+        <v>42795</v>
+      </c>
+      <c r="H5" s="6">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>4.3949999999999996E-3</v>
+      </c>
+      <c r="J5" s="5">
+        <v>7.9900000000000006E-3</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1.1586000000000001E-2</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1.4782E-2</v>
+      </c>
+      <c r="M5" s="5">
+        <v>1.5980999999999999E-2</v>
+      </c>
+      <c r="N5" s="5">
+        <v>1.7579000000000001E-2</v>
+      </c>
+      <c r="O5" s="5">
+        <v>2.0774999999999998E-2</v>
+      </c>
+      <c r="P5" s="5">
+        <v>2.3571999999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>42736</v>
       </c>
@@ -625,8 +6138,38 @@
       <c r="E6">
         <v>1.1158E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G6" s="3">
+        <v>42826</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>6.2059999999999997E-3</v>
+      </c>
+      <c r="J6" s="5">
+        <v>8.4220000000000007E-3</v>
+      </c>
+      <c r="K6" s="5">
+        <v>1.0194999999999999E-2</v>
+      </c>
+      <c r="L6" s="5">
+        <v>1.2855E-2</v>
+      </c>
+      <c r="M6" s="5">
+        <v>1.5514E-2</v>
+      </c>
+      <c r="N6" s="5">
+        <v>1.8617000000000002E-2</v>
+      </c>
+      <c r="O6" s="5">
+        <v>2.172E-2</v>
+      </c>
+      <c r="P6" s="5">
+        <v>2.4823000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>42736</v>
       </c>
@@ -642,8 +6185,38 @@
       <c r="E7">
         <v>1.2552000000000001E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G7" s="3">
+        <v>42856</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>4.6360000000000004E-3</v>
+      </c>
+      <c r="J7" s="5">
+        <v>9.273E-3</v>
+      </c>
+      <c r="K7" s="5">
+        <v>1.1591000000000001E-2</v>
+      </c>
+      <c r="L7" s="5">
+        <v>1.4199E-2</v>
+      </c>
+      <c r="M7" s="5">
+        <v>1.6517E-2</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1.9994000000000001E-2</v>
+      </c>
+      <c r="O7" s="5">
+        <v>2.1443E-2</v>
+      </c>
+      <c r="P7" s="5">
+        <v>2.3470999999999999E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>42736</v>
       </c>
@@ -659,8 +6232,38 @@
       <c r="E8">
         <v>1.6736000000000001E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G8" s="3">
+        <v>42887</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>4.9389999999999998E-3</v>
+      </c>
+      <c r="J8" s="5">
+        <v>8.5609999999999992E-3</v>
+      </c>
+      <c r="K8" s="5">
+        <v>1.2182999999999999E-2</v>
+      </c>
+      <c r="L8" s="5">
+        <v>1.4159E-2</v>
+      </c>
+      <c r="M8" s="5">
+        <v>1.7451000000000001E-2</v>
+      </c>
+      <c r="N8" s="5">
+        <v>2.0743999999999999E-2</v>
+      </c>
+      <c r="O8" s="5">
+        <v>2.3049E-2</v>
+      </c>
+      <c r="P8" s="5">
+        <v>2.4365999999999999E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>42736</v>
       </c>
@@ -676,8 +6279,38 @@
       <c r="E9">
         <v>1.6736000000000001E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G9" s="3">
+        <v>42917</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>5.3299999999999997E-3</v>
+      </c>
+      <c r="J9" s="5">
+        <v>8.5290000000000001E-3</v>
+      </c>
+      <c r="K9" s="5">
+        <v>1.0661E-2</v>
+      </c>
+      <c r="L9" s="5">
+        <v>1.3325999999999999E-2</v>
+      </c>
+      <c r="M9" s="5">
+        <v>1.5458E-2</v>
+      </c>
+      <c r="N9" s="5">
+        <v>1.8657E-2</v>
+      </c>
+      <c r="O9" s="5">
+        <v>1.9723000000000001E-2</v>
+      </c>
+      <c r="P9" s="5">
+        <v>2.1588E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>42736</v>
       </c>
@@ -693,8 +6326,38 @@
       <c r="E10">
         <v>1.8131000000000001E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G10" s="3">
+        <v>42948</v>
+      </c>
+      <c r="H10" s="6">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>6.9020000000000001E-3</v>
+      </c>
+      <c r="J10" s="5">
+        <v>1.0106E-2</v>
+      </c>
+      <c r="K10" s="5">
+        <v>1.2324E-2</v>
+      </c>
+      <c r="L10" s="5">
+        <v>1.5775000000000001E-2</v>
+      </c>
+      <c r="M10" s="5">
+        <v>2.0212000000000001E-2</v>
+      </c>
+      <c r="N10" s="5">
+        <v>2.2922999999999999E-2</v>
+      </c>
+      <c r="O10" s="5">
+        <v>2.4895E-2</v>
+      </c>
+      <c r="P10" s="5">
+        <v>2.5881000000000001E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>42767</v>
       </c>
@@ -710,8 +6373,38 @@
       <c r="E11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G11" s="3">
+        <v>42979</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>6.9930000000000001E-3</v>
+      </c>
+      <c r="J11" s="5">
+        <v>1.1988E-2</v>
+      </c>
+      <c r="K11" s="5">
+        <v>1.4486000000000001E-2</v>
+      </c>
+      <c r="L11" s="5">
+        <v>1.8232000000000002E-2</v>
+      </c>
+      <c r="M11" s="5">
+        <v>2.0230000000000001E-2</v>
+      </c>
+      <c r="N11" s="5">
+        <v>2.1728000000000001E-2</v>
+      </c>
+      <c r="O11" s="5">
+        <v>2.3477000000000001E-2</v>
+      </c>
+      <c r="P11" s="5">
+        <v>2.5974000000000001E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>42767</v>
       </c>
@@ -728,7 +6421,7 @@
         <v>1.843E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>42767</v>
       </c>
@@ -745,7 +6438,7 @@
         <v>4.914E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>42767</v>
       </c>
@@ -761,8 +6454,14 @@
       <c r="E14">
         <v>6.143E-3</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>42767</v>
       </c>
@@ -778,8 +6477,38 @@
       <c r="E15">
         <v>1.0442E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H15" s="1">
+        <v>42736</v>
+      </c>
+      <c r="I15" s="1">
+        <v>42767</v>
+      </c>
+      <c r="J15" s="1">
+        <v>42795</v>
+      </c>
+      <c r="K15" s="1">
+        <v>42826</v>
+      </c>
+      <c r="L15" s="1">
+        <v>42856</v>
+      </c>
+      <c r="M15" s="1">
+        <v>42887</v>
+      </c>
+      <c r="N15" s="1">
+        <v>42917</v>
+      </c>
+      <c r="O15" s="1">
+        <v>42948</v>
+      </c>
+      <c r="P15" s="1">
+        <v>42979</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>42767</v>
       </c>
@@ -795,8 +6524,38 @@
       <c r="E16">
         <v>1.1671000000000001E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G16" s="4">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6">
+        <v>0</v>
+      </c>
+      <c r="I16" s="6">
+        <v>0</v>
+      </c>
+      <c r="J16" s="6">
+        <v>0</v>
+      </c>
+      <c r="K16" s="6">
+        <v>0</v>
+      </c>
+      <c r="L16" s="6">
+        <v>0</v>
+      </c>
+      <c r="M16" s="6">
+        <v>0</v>
+      </c>
+      <c r="N16" s="6">
+        <v>0</v>
+      </c>
+      <c r="O16" s="6">
+        <v>0</v>
+      </c>
+      <c r="P16" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>42767</v>
       </c>
@@ -812,8 +6571,38 @@
       <c r="E17">
         <v>1.4128E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G17" s="4">
+        <v>1</v>
+      </c>
+      <c r="H17" s="5">
+        <v>2.7889999999999998E-3</v>
+      </c>
+      <c r="I17" s="5">
+        <v>1.843E-3</v>
+      </c>
+      <c r="J17" s="5">
+        <v>4.3949999999999996E-3</v>
+      </c>
+      <c r="K17" s="5">
+        <v>6.2059999999999997E-3</v>
+      </c>
+      <c r="L17" s="5">
+        <v>4.6360000000000004E-3</v>
+      </c>
+      <c r="M17" s="5">
+        <v>4.9389999999999998E-3</v>
+      </c>
+      <c r="N17" s="5">
+        <v>5.3299999999999997E-3</v>
+      </c>
+      <c r="O17" s="5">
+        <v>6.9020000000000001E-3</v>
+      </c>
+      <c r="P17" s="5">
+        <v>6.9930000000000001E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>42767</v>
       </c>
@@ -829,8 +6618,38 @@
       <c r="E18">
         <v>1.5356E-2</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G18" s="4">
+        <v>2</v>
+      </c>
+      <c r="H18" s="5">
+        <v>5.5789999999999998E-3</v>
+      </c>
+      <c r="I18" s="5">
+        <v>4.914E-3</v>
+      </c>
+      <c r="J18" s="5">
+        <v>7.9900000000000006E-3</v>
+      </c>
+      <c r="K18" s="5">
+        <v>8.4220000000000007E-3</v>
+      </c>
+      <c r="L18" s="5">
+        <v>9.273E-3</v>
+      </c>
+      <c r="M18" s="5">
+        <v>8.5609999999999992E-3</v>
+      </c>
+      <c r="N18" s="5">
+        <v>8.5290000000000001E-3</v>
+      </c>
+      <c r="O18" s="5">
+        <v>1.0106E-2</v>
+      </c>
+      <c r="P18" s="5">
+        <v>1.1988E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>42767</v>
       </c>
@@ -846,8 +6665,38 @@
       <c r="E19">
         <v>1.6584999999999999E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G19" s="4">
+        <v>3</v>
+      </c>
+      <c r="H19" s="5">
+        <v>6.9740000000000002E-3</v>
+      </c>
+      <c r="I19" s="5">
+        <v>6.143E-3</v>
+      </c>
+      <c r="J19" s="5">
+        <v>1.1586000000000001E-2</v>
+      </c>
+      <c r="K19" s="5">
+        <v>1.0194999999999999E-2</v>
+      </c>
+      <c r="L19" s="5">
+        <v>1.1591000000000001E-2</v>
+      </c>
+      <c r="M19" s="5">
+        <v>1.2182999999999999E-2</v>
+      </c>
+      <c r="N19" s="5">
+        <v>1.0661E-2</v>
+      </c>
+      <c r="O19" s="5">
+        <v>1.2324E-2</v>
+      </c>
+      <c r="P19" s="5">
+        <v>1.4486000000000001E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>42795</v>
       </c>
@@ -863,8 +6712,38 @@
       <c r="E20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G20" s="4">
+        <v>4</v>
+      </c>
+      <c r="H20" s="5">
+        <v>1.1158E-2</v>
+      </c>
+      <c r="I20" s="5">
+        <v>1.0442E-2</v>
+      </c>
+      <c r="J20" s="5">
+        <v>1.4782E-2</v>
+      </c>
+      <c r="K20" s="5">
+        <v>1.2855E-2</v>
+      </c>
+      <c r="L20" s="5">
+        <v>1.4199E-2</v>
+      </c>
+      <c r="M20" s="5">
+        <v>1.4159E-2</v>
+      </c>
+      <c r="N20" s="5">
+        <v>1.3325999999999999E-2</v>
+      </c>
+      <c r="O20" s="5">
+        <v>1.5775000000000001E-2</v>
+      </c>
+      <c r="P20" s="5">
+        <v>1.8232000000000002E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>42795</v>
       </c>
@@ -880,8 +6759,38 @@
       <c r="E21">
         <v>4.3949999999999996E-3</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G21" s="4">
+        <v>5</v>
+      </c>
+      <c r="H21" s="5">
+        <v>1.2552000000000001E-2</v>
+      </c>
+      <c r="I21" s="5">
+        <v>1.1671000000000001E-2</v>
+      </c>
+      <c r="J21" s="5">
+        <v>1.5980999999999999E-2</v>
+      </c>
+      <c r="K21" s="5">
+        <v>1.5514E-2</v>
+      </c>
+      <c r="L21" s="5">
+        <v>1.6517E-2</v>
+      </c>
+      <c r="M21" s="5">
+        <v>1.7451000000000001E-2</v>
+      </c>
+      <c r="N21" s="5">
+        <v>1.5458E-2</v>
+      </c>
+      <c r="O21" s="5">
+        <v>2.0212000000000001E-2</v>
+      </c>
+      <c r="P21" s="5">
+        <v>2.0230000000000001E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>42795</v>
       </c>
@@ -897,8 +6806,38 @@
       <c r="E22">
         <v>7.9900000000000006E-3</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G22" s="4">
+        <v>6</v>
+      </c>
+      <c r="H22" s="5">
+        <v>1.6736000000000001E-2</v>
+      </c>
+      <c r="I22" s="5">
+        <v>1.4128E-2</v>
+      </c>
+      <c r="J22" s="5">
+        <v>1.7579000000000001E-2</v>
+      </c>
+      <c r="K22" s="5">
+        <v>1.8617000000000002E-2</v>
+      </c>
+      <c r="L22" s="5">
+        <v>1.9994000000000001E-2</v>
+      </c>
+      <c r="M22" s="5">
+        <v>2.0743999999999999E-2</v>
+      </c>
+      <c r="N22" s="5">
+        <v>1.8657E-2</v>
+      </c>
+      <c r="O22" s="5">
+        <v>2.2922999999999999E-2</v>
+      </c>
+      <c r="P22" s="5">
+        <v>2.1728000000000001E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>42795</v>
       </c>
@@ -914,8 +6853,38 @@
       <c r="E23">
         <v>1.1586000000000001E-2</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G23" s="4">
+        <v>7</v>
+      </c>
+      <c r="H23" s="5">
+        <v>1.6736000000000001E-2</v>
+      </c>
+      <c r="I23" s="5">
+        <v>1.5356E-2</v>
+      </c>
+      <c r="J23" s="5">
+        <v>2.0774999999999998E-2</v>
+      </c>
+      <c r="K23" s="5">
+        <v>2.172E-2</v>
+      </c>
+      <c r="L23" s="5">
+        <v>2.1443E-2</v>
+      </c>
+      <c r="M23" s="5">
+        <v>2.3049E-2</v>
+      </c>
+      <c r="N23" s="5">
+        <v>1.9723000000000001E-2</v>
+      </c>
+      <c r="O23" s="5">
+        <v>2.4895E-2</v>
+      </c>
+      <c r="P23" s="5">
+        <v>2.3477000000000001E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>42795</v>
       </c>
@@ -931,8 +6900,38 @@
       <c r="E24">
         <v>1.4782E-2</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G24" s="4">
+        <v>8</v>
+      </c>
+      <c r="H24" s="5">
+        <v>1.8131000000000001E-2</v>
+      </c>
+      <c r="I24" s="5">
+        <v>1.6584999999999999E-2</v>
+      </c>
+      <c r="J24" s="5">
+        <v>2.3571999999999999E-2</v>
+      </c>
+      <c r="K24" s="5">
+        <v>2.4823000000000001E-2</v>
+      </c>
+      <c r="L24" s="5">
+        <v>2.3470999999999999E-2</v>
+      </c>
+      <c r="M24" s="5">
+        <v>2.4365999999999999E-2</v>
+      </c>
+      <c r="N24" s="5">
+        <v>2.1588E-2</v>
+      </c>
+      <c r="O24" s="5">
+        <v>2.5881000000000001E-2</v>
+      </c>
+      <c r="P24" s="5">
+        <v>2.5974000000000001E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>42795</v>
       </c>
@@ -949,7 +6948,7 @@
         <v>1.5980999999999999E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>42795</v>
       </c>
@@ -966,7 +6965,7 @@
         <v>1.7579000000000001E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>42795</v>
       </c>
@@ -983,7 +6982,7 @@
         <v>2.0774999999999998E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>42795</v>
       </c>
@@ -1000,7 +6999,7 @@
         <v>2.3571999999999999E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>42826</v>
       </c>
@@ -1017,7 +7016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>42826</v>
       </c>
@@ -1034,7 +7033,7 @@
         <v>6.2059999999999997E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>42826</v>
       </c>
@@ -1051,7 +7050,7 @@
         <v>8.4220000000000007E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>42826</v>
       </c>
@@ -1919,9 +7918,34 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting pivot="1" sqref="H17:P24">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting pivot="1" sqref="I3:P11">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
